--- a/스마트점핑_DB.xlsx
+++ b/스마트점핑_DB.xlsx
@@ -2670,7 +2670,7 @@
         <v>03ac674216f3e15c761ee1a5e255f067953623c8b388b4459e13f978d7c846f4</v>
       </c>
       <c r="C2" t="str">
-        <v>김현주</v>
+        <v>테스트</v>
       </c>
       <c r="D2" t="str">
         <v>강동초등학교</v>
@@ -3138,7 +3138,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-22 11:47:25</v>
+        <v>2026-08-22 13:14:36</v>
       </c>
     </row>
     <row r="3">
@@ -3158,7 +3158,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-22 11:47:25</v>
+        <v>2026-08-22 13:14:36</v>
       </c>
     </row>
   </sheetData>

--- a/스마트점핑_DB.xlsx
+++ b/스마트점핑_DB.xlsx
@@ -2690,7 +2690,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>admin</v>
+        <v>test</v>
       </c>
       <c r="B3" t="str">
         <v>03ac674216f3e15c761ee1a5e255f067953623c8b388b4459e13f978d7c846f4</v>
@@ -3138,7 +3138,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-22 13:14:36</v>
+        <v>2026-08-22 13:19:19</v>
       </c>
     </row>
     <row r="3">
@@ -3158,7 +3158,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-22 13:14:36</v>
+        <v>2026-08-22 13:19:19</v>
       </c>
     </row>
   </sheetData>

--- a/스마트점핑_DB.xlsx
+++ b/스마트점핑_DB.xlsx
@@ -2624,7 +2624,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -2714,9 +2714,35 @@
         <v>정상</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>teststu</v>
+      </c>
+      <c r="B4" t="str">
+        <v>03ac674216f3e15c761ee1a5e255f067953623c8b388b4459e13f978d7c846f4</v>
+      </c>
+      <c r="C4" t="str">
+        <v>학생</v>
+      </c>
+      <c r="D4" t="str">
+        <v>강동초등학교 3학년 2반</v>
+      </c>
+      <c r="E4" t="str">
+        <v>울산광역시 북구</v>
+      </c>
+      <c r="F4" t="str">
+        <v>학생</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="H4" t="str">
+        <v>정상</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3138,7 +3164,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-22 13:19:19</v>
+        <v>2026-08-22 13:56:09</v>
       </c>
     </row>
     <row r="3">
@@ -3158,7 +3184,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-22 13:19:19</v>
+        <v>2026-08-22 13:56:09</v>
       </c>
     </row>
   </sheetData>

--- a/스마트점핑_DB.xlsx
+++ b/스마트점핑_DB.xlsx
@@ -2673,13 +2673,13 @@
         <v>테스트</v>
       </c>
       <c r="D2" t="str">
-        <v>강동초등학교</v>
+        <v>스마트점핑 본부</v>
       </c>
       <c r="E2" t="str">
         <v>울산광역시 북구</v>
       </c>
       <c r="F2" t="str">
-        <v>교사</v>
+        <v>관리자</v>
       </c>
       <c r="G2" t="str">
         <v>2026-08-22</v>
@@ -2696,16 +2696,16 @@
         <v>03ac674216f3e15c761ee1a5e255f067953623c8b388b4459e13f978d7c846f4</v>
       </c>
       <c r="C3" t="str">
-        <v>관리자</v>
+        <v>교사</v>
       </c>
       <c r="D3" t="str">
-        <v>스마트점핑 본부</v>
+        <v>옥동초등학교</v>
       </c>
       <c r="E3" t="str">
-        <v>서울특별시</v>
+        <v>울산광역시 남구</v>
       </c>
       <c r="F3" t="str">
-        <v>관리자</v>
+        <v>교사</v>
       </c>
       <c r="G3" t="str">
         <v>2026-08-22</v>
@@ -2883,7 +2883,7 @@
         <v>CL004</v>
       </c>
       <c r="B5" t="str">
-        <v>teacher</v>
+        <v>test</v>
       </c>
       <c r="C5" t="str">
         <v>2026-08</v>
@@ -2912,7 +2912,7 @@
         <v>CL005</v>
       </c>
       <c r="B6" t="str">
-        <v>teacher</v>
+        <v>test</v>
       </c>
       <c r="C6" t="str">
         <v>2026-07</v>
@@ -2941,7 +2941,7 @@
         <v>CL006</v>
       </c>
       <c r="B7" t="str">
-        <v>teacher</v>
+        <v>test</v>
       </c>
       <c r="C7" t="str">
         <v>2026-08</v>
@@ -3117,7 +3117,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -3164,7 +3164,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-22 13:56:09</v>
+        <v>2026-08-22 14:16:53</v>
       </c>
     </row>
     <row r="3">
@@ -3184,12 +3184,32 @@
         <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-22 13:56:09</v>
+        <v>2026-08-22 14:16:53</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>test</v>
+      </c>
+      <c r="B4" t="str">
+        <v>스마트점핑 로프 (학급용)</v>
+      </c>
+      <c r="C4" t="str">
+        <v>울산대리점</v>
+      </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-08-22 14:16:53</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3248,7 +3268,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>teacher</v>
+        <v>test</v>
       </c>
       <c r="B4" t="str">
         <v>체력왕 도전</v>

--- a/스마트점핑_DB.xlsx
+++ b/스마트점핑_DB.xlsx
@@ -405,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G24"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -459,7 +459,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>N</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -487,25 +487,25 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>C2</v>
+        <v>C1</v>
       </c>
       <c r="B4" t="str">
-        <v>시간타이머</v>
+        <v>명상</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="str">
-        <v>S21</v>
+        <v>S13</v>
       </c>
       <c r="E4" t="str">
-        <v>휴식영상 타이머</v>
+        <v>어린이 명상</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>N</v>
       </c>
     </row>
     <row r="5">
@@ -519,13 +519,13 @@
         <v>2</v>
       </c>
       <c r="D5" t="str">
-        <v>S22</v>
+        <v>S21</v>
       </c>
       <c r="E5" t="str">
-        <v>카운터 타이머</v>
+        <v>휴식영상 타이머</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -533,22 +533,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="B6" t="str">
-        <v>준비운동 | 타바타</v>
+        <v>시간타이머</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="str">
-        <v>S31</v>
+        <v>S22</v>
       </c>
       <c r="E6" t="str">
-        <v>몸풀기 &amp; 스트레칭</v>
+        <v>카운터 타이머</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="str">
         <v>N</v>
@@ -565,16 +565,16 @@
         <v>3</v>
       </c>
       <c r="D7" t="str">
-        <v>S32</v>
+        <v>S31</v>
       </c>
       <c r="E7" t="str">
-        <v>타바타 &amp; 기초체력</v>
+        <v>몸풀기 &amp; 스트레칭</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v>N</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="str">
-        <v>S33</v>
+        <v>S32</v>
       </c>
       <c r="E8" t="str">
-        <v>기초체력 추천 조합</v>
+        <v>타바타 &amp; 기초체력</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -611,13 +611,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="str">
-        <v>S34</v>
+        <v>S33</v>
       </c>
       <c r="E9" t="str">
-        <v>점핑 근력운동</v>
+        <v>기초체력 추천 조합</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -625,22 +625,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="B10" t="str">
-        <v>스마트점핑</v>
+        <v>준비운동 | 타바타</v>
       </c>
       <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="str">
+        <v>S34</v>
+      </c>
+      <c r="E10" t="str">
+        <v>점핑 근력운동</v>
+      </c>
+      <c r="F10">
         <v>4</v>
-      </c>
-      <c r="D10" t="str">
-        <v>S41</v>
-      </c>
-      <c r="E10" t="str">
-        <v>급수 친구들 1단계 [브로빗]</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -648,48 +648,48 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="B11" t="str">
-        <v>스마트점핑</v>
+        <v>준비운동 | 타바타</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="str">
-        <v>S42</v>
+        <v>S35</v>
       </c>
       <c r="E11" t="str">
-        <v>급수 친구들 2단계 [월라비]</v>
+        <v>정리운동 · 쿨다운</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>N</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="B12" t="str">
-        <v>스마트점핑</v>
+        <v>준비운동 | 타바타</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="str">
-        <v>S43</v>
+        <v>S36</v>
       </c>
       <c r="E12" t="str">
-        <v>급수 친구들 3단계 [이글]</v>
+        <v>레크리에이션 놀이</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>N</v>
       </c>
     </row>
     <row r="13">
@@ -703,16 +703,16 @@
         <v>4</v>
       </c>
       <c r="D13" t="str">
-        <v>S44</v>
+        <v>S41</v>
       </c>
       <c r="E13" t="str">
-        <v>쌩쌩이 · 2단뛰기</v>
+        <v>급수 친구들 1단계 [브로빗]</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G13" t="str">
-        <v>N</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -726,13 +726,13 @@
         <v>4</v>
       </c>
       <c r="D14" t="str">
-        <v>S45</v>
+        <v>S42</v>
       </c>
       <c r="E14" t="str">
-        <v>응용 · 심화</v>
+        <v>급수 친구들 2단계 [월라비]</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -749,13 +749,13 @@
         <v>4</v>
       </c>
       <c r="D15" t="str">
-        <v>S46</v>
+        <v>S43</v>
       </c>
       <c r="E15" t="str">
-        <v>[지도자 필수교육]</v>
+        <v>급수 친구들 3단계 [이글]</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -763,106 +763,221 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>C5</v>
+        <v>C4</v>
       </c>
       <c r="B16" t="str">
-        <v>비트 트레이닝</v>
+        <v>스마트점핑</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="str">
-        <v>S51</v>
+        <v>S44</v>
       </c>
       <c r="E16" t="str">
-        <v>동요 율동</v>
+        <v>쌩쌩이 · 2단뛰기</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G16" t="str">
-        <v>N</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>C5</v>
+        <v>C4</v>
       </c>
       <c r="B17" t="str">
-        <v>비트 트레이닝</v>
+        <v>스마트점핑</v>
       </c>
       <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17" t="str">
+        <v>S45</v>
+      </c>
+      <c r="E17" t="str">
+        <v>음악줄넘기</v>
+      </c>
+      <c r="F17">
         <v>5</v>
       </c>
-      <c r="D17" t="str">
-        <v>S52</v>
-      </c>
-      <c r="E17" t="str">
-        <v>체조 메들리</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
       <c r="G17" t="str">
-        <v/>
+        <v>N</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>C6</v>
+        <v>C4</v>
       </c>
       <c r="B18" t="str">
-        <v>Killing Time Zone</v>
+        <v>스마트점핑</v>
       </c>
       <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18" t="str">
+        <v>S46</v>
+      </c>
+      <c r="E18" t="str">
+        <v>[지도자 필수교육]</v>
+      </c>
+      <c r="F18">
         <v>6</v>
       </c>
-      <c r="D18" t="str">
-        <v>S61</v>
-      </c>
-      <c r="E18" t="str">
-        <v>나라별 국기맞추기</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
       <c r="G18" t="str">
-        <v>N</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
+        <v>C5</v>
+      </c>
+      <c r="B19" t="str">
+        <v>비트 트레이닝</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19" t="str">
+        <v>S51</v>
+      </c>
+      <c r="E19" t="str">
+        <v>동요 율동</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>C5</v>
+      </c>
+      <c r="B20" t="str">
+        <v>비트 트레이닝</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+      <c r="D20" t="str">
+        <v>S52</v>
+      </c>
+      <c r="E20" t="str">
+        <v>체조 메들리</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>C5</v>
+      </c>
+      <c r="B21" t="str">
+        <v>비트 트레이닝</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21" t="str">
+        <v>S53</v>
+      </c>
+      <c r="E21" t="str">
+        <v>K-POP 키즈댄스</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21" t="str">
+        <v>N</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
         <v>C6</v>
       </c>
-      <c r="B19" t="str">
+      <c r="B22" t="str">
         <v>Killing Time Zone</v>
       </c>
-      <c r="C19">
+      <c r="C22">
         <v>6</v>
       </c>
-      <c r="D19" t="str">
+      <c r="D22" t="str">
+        <v>S61</v>
+      </c>
+      <c r="E22" t="str">
+        <v>나라별 국기맞추기</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>C6</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Killing Time Zone</v>
+      </c>
+      <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23" t="str">
         <v>S62</v>
       </c>
-      <c r="E19" t="str">
-        <v>숨은그림 찾기</v>
-      </c>
-      <c r="F19">
+      <c r="E23" t="str">
+        <v>숨은그림 · 틀린그림 찾기</v>
+      </c>
+      <c r="F23">
         <v>2</v>
       </c>
-      <c r="G19" t="str">
+      <c r="G23" t="str">
+        <v>N</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>C6</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Killing Time Zone</v>
+      </c>
+      <c r="C24">
+        <v>6</v>
+      </c>
+      <c r="D24" t="str">
+        <v>S63</v>
+      </c>
+      <c r="E24" t="str">
+        <v>넌센스 퀴즈</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" t="str">
         <v>N</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G24"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I105"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -944,13 +1059,13 @@
         <v>S11</v>
       </c>
       <c r="D3" t="str">
-        <v>들숨날숨 호흡연습 1단계 (5분 명상) / 마음챙김 기초명상, 쉬운명상</v>
+        <v>마음이 차분해지는 5분 호흡운동 | 브레스워크 | 명상 | 잠 잘 오는 명상 | 편안해지는 명상 | 휴식 명상</v>
       </c>
       <c r="E3" t="str">
-        <v>RJO2qgqVol0</v>
+        <v>bG4e-HnlJTE</v>
       </c>
       <c r="F3" t="str">
-        <v>05:17</v>
+        <v>10:17</v>
       </c>
       <c r="G3">
         <v>2062</v>
@@ -973,13 +1088,13 @@
         <v>S11</v>
       </c>
       <c r="D4" t="str">
-        <v>5분 호흡명상 - 뇌를 위한 최고의 휴식법 (스트레스 해소, 뇌 피로회복)</v>
+        <v>들숨날숨 호흡연습 1단계 (5분 명상) / 마음챙김 기초명상, 쉬운명상</v>
       </c>
       <c r="E4" t="str">
-        <v>dZewQEbQQM0</v>
+        <v>RJO2qgqVol0</v>
       </c>
       <c r="F4" t="str">
-        <v>07:13</v>
+        <v>05:17</v>
       </c>
       <c r="G4">
         <v>3033</v>
@@ -999,16 +1114,16 @@
         <v>C1</v>
       </c>
       <c r="C5" t="str">
-        <v>S12</v>
+        <v>S11</v>
       </c>
       <c r="D5" t="str">
-        <v>마음이 차분해지는 5분 호흡운동 | 브레스워크 | 명상 | 잠 잘 오는 명상 | 편안해지는 명상 | 휴식 명상</v>
+        <v>5분 호흡명상 - 뇌를 위한 최고의 휴식법 (스트레스 해소, 뇌 피로회복)</v>
       </c>
       <c r="E5" t="str">
-        <v>bG4e-HnlJTE</v>
+        <v>dZewQEbQQM0</v>
       </c>
       <c r="F5" t="str">
-        <v>10:17</v>
+        <v>07:13</v>
       </c>
       <c r="G5">
         <v>4004</v>
@@ -1028,16 +1143,16 @@
         <v>C1</v>
       </c>
       <c r="C6" t="str">
-        <v>S12</v>
+        <v>S11</v>
       </c>
       <c r="D6" t="str">
-        <v>마음챙김 - 호흡 명상</v>
+        <v>[처음 만나는 마음챙김 명상] 안희영 소장과 쉽게 배워보는 '호흡 마음챙김명상'</v>
       </c>
       <c r="E6" t="str">
-        <v>tNao3xp5yjM</v>
+        <v>H8DIbAhJ8fg</v>
       </c>
       <c r="F6" t="str">
-        <v>01:42</v>
+        <v>14:55</v>
       </c>
       <c r="G6">
         <v>4975</v>
@@ -1054,19 +1169,19 @@
         <v>V0006</v>
       </c>
       <c r="B7" t="str">
-        <v>C2</v>
+        <v>C1</v>
       </c>
       <c r="C7" t="str">
-        <v>S21</v>
+        <v>S12</v>
       </c>
       <c r="D7" t="str">
-        <v>5분 타이머 편안한 숲 힐링타임 - 5 Minute Countdown Timer with Forest</v>
+        <v>마음챙김 - 호흡 명상</v>
       </c>
       <c r="E7" t="str">
-        <v>119KVJumA1M</v>
+        <v>tNao3xp5yjM</v>
       </c>
       <c r="F7" t="str">
-        <v>05:03</v>
+        <v>01:42</v>
       </c>
       <c r="G7">
         <v>5946</v>
@@ -1083,19 +1198,19 @@
         <v>V0007</v>
       </c>
       <c r="B8" t="str">
-        <v>C2</v>
+        <v>C1</v>
       </c>
       <c r="C8" t="str">
-        <v>S21</v>
+        <v>S12</v>
       </c>
       <c r="D8" t="str">
-        <v>⏰⌛5분 타이머 | 5분 카운트 다운 | 5분 휴식시간 | 5분 쉬는시간 | 배경음악</v>
+        <v>제주특별자치도교육청 학생건강증진추진단 마음챙김 애니메이션 초등3편 - 감정 마음챙김 _  #명상 #초등 #호흡 #건강 #제주교육 #감정</v>
       </c>
       <c r="E8" t="str">
-        <v>mIYObGZ1I_w</v>
+        <v>uVlUn_c1Xew</v>
       </c>
       <c r="F8" t="str">
-        <v>05:05</v>
+        <v>05:42</v>
       </c>
       <c r="G8">
         <v>6917</v>
@@ -1112,19 +1227,19 @@
         <v>V0008</v>
       </c>
       <c r="B9" t="str">
-        <v>C2</v>
+        <v>C1</v>
       </c>
       <c r="C9" t="str">
-        <v>S22</v>
+        <v>S13</v>
       </c>
       <c r="D9" t="str">
-        <v>5 minute timer with music 타이머 5분 카운트다운 countdown</v>
+        <v>초등학생을 위한 소리 듣기 명상 | 어린이 명상 | 마보</v>
       </c>
       <c r="E9" t="str">
-        <v>qIiMFZ88NDI</v>
+        <v>nIICI7cSSUM</v>
       </c>
       <c r="F9" t="str">
-        <v>05:03</v>
+        <v>03:57</v>
       </c>
       <c r="G9">
         <v>7888</v>
@@ -1141,19 +1256,19 @@
         <v>V0009</v>
       </c>
       <c r="B10" t="str">
-        <v>C2</v>
+        <v>C1</v>
       </c>
       <c r="C10" t="str">
-        <v>S22</v>
+        <v>S13</v>
       </c>
       <c r="D10" t="str">
-        <v>5분 알람 타이머 (카운트다운)</v>
+        <v>🌊어린이 1분 바다명상🌊가장 쉽고 재미있는 명상 - 집중력, 기억력, 행복, 사랑, 자아, 긍정, 감사, 끈기, 인내, 자기조절능력 키우기 명상</v>
       </c>
       <c r="E10" t="str">
-        <v>Byzwstv74Xw</v>
+        <v>8H44pw20-74</v>
       </c>
       <c r="F10" t="str">
-        <v>05:16</v>
+        <v>03:49</v>
       </c>
       <c r="G10">
         <v>8859</v>
@@ -1170,19 +1285,19 @@
         <v>V0010</v>
       </c>
       <c r="B11" t="str">
-        <v>C2</v>
+        <v>C1</v>
       </c>
       <c r="C11" t="str">
-        <v>S22</v>
+        <v>S13</v>
       </c>
       <c r="D11" t="str">
-        <v>[5분 타이머] 5minute countdown mineetimer with alarm</v>
+        <v>[홍익학당] 어린이 숫자명상</v>
       </c>
       <c r="E11" t="str">
-        <v>0fZC2y5pCck</v>
+        <v>LjQ0HhOLkuk</v>
       </c>
       <c r="F11" t="str">
-        <v>05:11</v>
+        <v>02:08</v>
       </c>
       <c r="G11">
         <v>430</v>
@@ -1199,19 +1314,19 @@
         <v>V0011</v>
       </c>
       <c r="B12" t="str">
-        <v>C2</v>
+        <v>C1</v>
       </c>
       <c r="C12" t="str">
-        <v>S22</v>
+        <v>S13</v>
       </c>
       <c r="D12" t="str">
-        <v>5 minute timerㅣ 5분타이머ㅣ봄맞이5분타이머ㅣ정리정돈음악 ㅣ생활습관타이머 ㅣㅣ 교실타이머 ㅣ5minute countdown timer</v>
+        <v>Me-time 어린이 가을훈련 - 어린이 5분명상(Ver. 대각지)</v>
       </c>
       <c r="E12" t="str">
-        <v>ec3vEdyG8oI</v>
+        <v>WVBh1C-bRbo</v>
       </c>
       <c r="F12" t="str">
-        <v>05:23</v>
+        <v>08:20</v>
       </c>
       <c r="G12">
         <v>1401</v>
@@ -1231,16 +1346,16 @@
         <v>C2</v>
       </c>
       <c r="C13" t="str">
-        <v>S22</v>
+        <v>S21</v>
       </c>
       <c r="D13" t="str">
-        <v>5분 타이머</v>
+        <v>5분 타이머 편안한 숲 힐링타임 - 5 Minute Countdown Timer with Forest</v>
       </c>
       <c r="E13" t="str">
-        <v>CXV_DqsWSPU</v>
+        <v>119KVJumA1M</v>
       </c>
       <c r="F13" t="str">
-        <v>05:05</v>
+        <v>05:03</v>
       </c>
       <c r="G13">
         <v>2372</v>
@@ -1260,16 +1375,16 @@
         <v>C2</v>
       </c>
       <c r="C14" t="str">
-        <v>S22</v>
+        <v>S21</v>
       </c>
       <c r="D14" t="str">
-        <v>Countdown For 5 Minutes</v>
+        <v>⏰⌛5분 타이머 | 5분 카운트 다운 | 5분 휴식시간 | 5분 쉬는시간 | 배경음악</v>
       </c>
       <c r="E14" t="str">
-        <v>3dJ4wFqQzz4</v>
+        <v>mIYObGZ1I_w</v>
       </c>
       <c r="F14" t="str">
-        <v>05:10</v>
+        <v>05:05</v>
       </c>
       <c r="G14">
         <v>3343</v>
@@ -1286,19 +1401,19 @@
         <v>V0014</v>
       </c>
       <c r="B15" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C15" t="str">
-        <v>S31</v>
+        <v>S21</v>
       </c>
       <c r="D15" t="str">
-        <v>교실체육 전 3분 워밍업 (준비운동 | 스트레칭 | 교실 체력 트레이닝  )</v>
+        <v>[10분]귀여운 고양이 타이머/3분,1분 중간 알람/10minute timer</v>
       </c>
       <c r="E15" t="str">
-        <v>hMCvvDHB46o</v>
+        <v>pZnefFq4aDk</v>
       </c>
       <c r="F15" t="str">
-        <v>03:07</v>
+        <v>10:20</v>
       </c>
       <c r="G15">
         <v>4314</v>
@@ -1315,19 +1430,19 @@
         <v>V0015</v>
       </c>
       <c r="B16" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C16" t="str">
-        <v>S31</v>
+        <v>S21</v>
       </c>
       <c r="D16" t="str">
-        <v>[서초초등체육교실 시즌3] 준비운동</v>
+        <v>타이머 10분,  알람 10분 우리나라 수업, 정리 타이머 10 min Timer, 징소리 카운트다운</v>
       </c>
       <c r="E16" t="str">
-        <v>ZmUj-E9A44E</v>
+        <v>w0OHKiIV44E</v>
       </c>
       <c r="F16" t="str">
-        <v>04:43</v>
+        <v>10:08</v>
       </c>
       <c r="G16">
         <v>5285</v>
@@ -1344,19 +1459,19 @@
         <v>V0016</v>
       </c>
       <c r="B17" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C17" t="str">
-        <v>S31</v>
+        <v>S22</v>
       </c>
       <c r="D17" t="str">
-        <v>온라인 체육 수업 - 5분 스트레칭 [준비운동]</v>
+        <v>5 minute timer with music 타이머 5분 카운트다운 countdown</v>
       </c>
       <c r="E17" t="str">
-        <v>PFJe9i9UbZ4</v>
+        <v>qIiMFZ88NDI</v>
       </c>
       <c r="F17" t="str">
-        <v>05:09</v>
+        <v>05:03</v>
       </c>
       <c r="G17">
         <v>6256</v>
@@ -1373,19 +1488,19 @@
         <v>V0017</v>
       </c>
       <c r="B18" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C18" t="str">
-        <v>S31</v>
+        <v>S22</v>
       </c>
       <c r="D18" t="str">
-        <v>의자 앉아 맨손체조ㅣ책상 스트레칭ㅣ의자 스트레칭ㅣ교실 스트레칭ㅣ놀이 준비운동ㅣ쏭쌤TV</v>
+        <v>5분 알람 타이머 (카운트다운)</v>
       </c>
       <c r="E18" t="str">
-        <v>2lru6IsOQ6Y</v>
+        <v>Byzwstv74Xw</v>
       </c>
       <c r="F18" t="str">
-        <v>04:05</v>
+        <v>05:16</v>
       </c>
       <c r="G18">
         <v>7227</v>
@@ -1402,19 +1517,19 @@
         <v>V0018</v>
       </c>
       <c r="B19" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C19" t="str">
-        <v>S31</v>
+        <v>S22</v>
       </c>
       <c r="D19" t="str">
-        <v>체육 수업 준비운동 및 정리운동 - 기백반 체육교실의 일상적인 준비운동 따라하기</v>
+        <v>[5분 타이머] 5minute countdown mineetimer with alarm</v>
       </c>
       <c r="E19" t="str">
-        <v>erMfzZ5_or8</v>
+        <v>0fZC2y5pCck</v>
       </c>
       <c r="F19" t="str">
-        <v>05:29</v>
+        <v>05:11</v>
       </c>
       <c r="G19">
         <v>8198</v>
@@ -1431,19 +1546,19 @@
         <v>V0019</v>
       </c>
       <c r="B20" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C20" t="str">
-        <v>S31</v>
+        <v>S22</v>
       </c>
       <c r="D20" t="str">
-        <v>3분, 초간단 운동 전 워밍업 스트레칭(부상 예방, 운동효과 대박, 가동범위 증가)</v>
+        <v>5 minute timerㅣ 5분타이머ㅣ봄맞이5분타이머ㅣ정리정돈음악 ㅣ생활습관타이머 ㅣㅣ 교실타이머 ㅣ5minute countdown timer</v>
       </c>
       <c r="E20" t="str">
-        <v>8qf727092l4</v>
+        <v>ec3vEdyG8oI</v>
       </c>
       <c r="F20" t="str">
-        <v>03:29</v>
+        <v>05:23</v>
       </c>
       <c r="G20">
         <v>9169</v>
@@ -1460,19 +1575,19 @@
         <v>V0020</v>
       </c>
       <c r="B21" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C21" t="str">
-        <v>S32</v>
+        <v>S22</v>
       </c>
       <c r="D21" t="str">
-        <v>[마포구체육회]홈트레이닝/칼로리 폭파 4분 타바타</v>
+        <v>5분 타이머</v>
       </c>
       <c r="E21" t="str">
-        <v>G9p1ZehAAnI</v>
+        <v>CXV_DqsWSPU</v>
       </c>
       <c r="F21" t="str">
-        <v>04:38</v>
+        <v>05:05</v>
       </c>
       <c r="G21">
         <v>740</v>
@@ -1489,19 +1604,19 @@
         <v>V0021</v>
       </c>
       <c r="B22" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C22" t="str">
-        <v>S32</v>
+        <v>S22</v>
       </c>
       <c r="D22" t="str">
-        <v>체지방↓DOWN, 근력↑UP "4분 타바타 홈트레이닝" (초보자,중상급자 모두가능!)</v>
+        <v>Countdown For 5 Minutes</v>
       </c>
       <c r="E22" t="str">
-        <v>BL8kwdj-XWU</v>
+        <v>3dJ4wFqQzz4</v>
       </c>
       <c r="F22" t="str">
-        <v>05:54</v>
+        <v>05:10</v>
       </c>
       <c r="G22">
         <v>1711</v>
@@ -1518,19 +1633,19 @@
         <v>V0022</v>
       </c>
       <c r="B23" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C23" t="str">
-        <v>S32</v>
+        <v>S22</v>
       </c>
       <c r="D23" t="str">
-        <v>집에서 누구나 [4분 타바타] 1편 / 화성시문화재단과 홈트레이닝하기</v>
+        <v>3분 알람 타이머 (카운트다운)</v>
       </c>
       <c r="E23" t="str">
-        <v>RFFWIbUcBXo</v>
+        <v>fJMgbAw_sAI</v>
       </c>
       <c r="F23" t="str">
-        <v>10:42</v>
+        <v>03:16</v>
       </c>
       <c r="G23">
         <v>2682</v>
@@ -1547,19 +1662,19 @@
         <v>V0023</v>
       </c>
       <c r="B24" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C24" t="str">
-        <v>S32</v>
+        <v>S22</v>
       </c>
       <c r="D24" t="str">
-        <v>운동초보에게 딱! 홈트 4분 타바타운동으로 저질체력 탈출해보자! | Low physical fitness? You can change it! Tabata for beginner</v>
+        <v>⏰⌛1분 타이머 | 1분 카운트 다운 | 1분 휴식시간 | 1분 쉬는시간 | 배경음악</v>
       </c>
       <c r="E24" t="str">
-        <v>BxElnlkcfts</v>
+        <v>-bobh50VdbA</v>
       </c>
       <c r="F24" t="str">
-        <v>04:35</v>
+        <v>01:20</v>
       </c>
       <c r="G24">
         <v>3653</v>
@@ -1576,19 +1691,19 @@
         <v>V0024</v>
       </c>
       <c r="B25" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C25" t="str">
-        <v>S32</v>
+        <v>S22</v>
       </c>
       <c r="D25" t="str">
-        <v>[실전]하루 4분 체지방 태우기 운동 - 집에서 하는 다이어트 타바타 운동 5 [핏분 유쾌한 홈트레이닝]</v>
+        <v>1분 타이머 / 1분 카운트 다운 / 1분 알람</v>
       </c>
       <c r="E25" t="str">
-        <v>ta-Uq_prRT8</v>
+        <v>KEwM1DMZoo8</v>
       </c>
       <c r="F25" t="str">
-        <v>06:34</v>
+        <v>22:23</v>
       </c>
       <c r="G25">
         <v>4624</v>
@@ -1605,19 +1720,19 @@
         <v>V0025</v>
       </c>
       <c r="B26" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C26" t="str">
-        <v>S33</v>
+        <v>S22</v>
       </c>
       <c r="D26" t="str">
-        <v>뱃살 빼는 최고의 운동 ! 4분 쉬지 않고 (신 타바타 버전)ㅣ고민수</v>
+        <v>10분 알람 타이머 (카운트다운)</v>
       </c>
       <c r="E26" t="str">
-        <v>EPXeswXkJDg</v>
+        <v>PiU0fht2ENE</v>
       </c>
       <c r="F26" t="str">
-        <v>06:27</v>
+        <v>10:16</v>
       </c>
       <c r="G26">
         <v>5595</v>
@@ -1634,19 +1749,19 @@
         <v>V0026</v>
       </c>
       <c r="B27" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C27" t="str">
-        <v>S33</v>
+        <v>S22</v>
       </c>
       <c r="D27" t="str">
-        <v>4분 운동으로 1시간 운동효과 ? 타바타 전신편 !/ 홈트레이닝</v>
+        <v>이동시간ㅣ3분 타이머ㅣ특별실 이동ㅣ정리 정돈ㅣ질서를 지켜 줄 서기ㅣ학급경영ㅣ쏭쌤TV</v>
       </c>
       <c r="E27" t="str">
-        <v>4deNtH6p2U0</v>
+        <v>1RZd1U8uGR8</v>
       </c>
       <c r="F27" t="str">
-        <v>04:24</v>
+        <v>03:06</v>
       </c>
       <c r="G27">
         <v>6566</v>
@@ -1663,19 +1778,19 @@
         <v>V0027</v>
       </c>
       <c r="B28" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C28" t="str">
-        <v>S33</v>
+        <v>S22</v>
       </c>
       <c r="D28" t="str">
-        <v>Day35 하루 4분 홈트 타바타운동(8가지 코어 등척성운동 )</v>
+        <v>3분 타이머 / 3분 카운트다운 / 3분 알람</v>
       </c>
       <c r="E28" t="str">
-        <v>esPoIcFC_T4</v>
+        <v>Zgn93PpZUg8</v>
       </c>
       <c r="F28" t="str">
-        <v>06:08</v>
+        <v>30:10</v>
       </c>
       <c r="G28">
         <v>7537</v>
@@ -1692,19 +1807,19 @@
         <v>V0028</v>
       </c>
       <c r="B29" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C29" t="str">
-        <v>S34</v>
+        <v>S22</v>
       </c>
       <c r="D29" t="str">
-        <v>쳐진 엉덩이 올리는 4분 타바타 운동 (홈트레이닝)ㅣ고민수</v>
+        <v>10분 - 타이머&amp;알람 (10분 카운트다운 타이머) │시작음:또로롱 / 중간소리:없음 / 종료음:알람소리</v>
       </c>
       <c r="E29" t="str">
-        <v>AytACfar2AI</v>
+        <v>LE0RWymF1Vc</v>
       </c>
       <c r="F29" t="str">
-        <v>09:18</v>
+        <v>10:12</v>
       </c>
       <c r="G29">
         <v>8508</v>
@@ -1721,19 +1836,19 @@
         <v>V0029</v>
       </c>
       <c r="B30" t="str">
-        <v>C3</v>
+        <v>C2</v>
       </c>
       <c r="C30" t="str">
-        <v>S34</v>
+        <v>S22</v>
       </c>
       <c r="D30" t="str">
-        <v>[주원홈트] 준비운동 스트레칭 - 운동 전에는 꼭 따라해야 하는 워밍업 영상</v>
+        <v>[Timer][10minutes][타이머][10분]/[카운트다운]/[그라데이션][다크그레이배경][마감소리][나머지무음]</v>
       </c>
       <c r="E30" t="str">
-        <v>2oN6SFl85VY</v>
+        <v>uPSoj0_OW9A</v>
       </c>
       <c r="F30" t="str">
-        <v>06:24</v>
+        <v>10:20</v>
       </c>
       <c r="G30">
         <v>9479</v>
@@ -1753,16 +1868,16 @@
         <v>C3</v>
       </c>
       <c r="C31" t="str">
-        <v>S34</v>
+        <v>S31</v>
       </c>
       <c r="D31" t="str">
-        <v>하루를 이 동작으로 시작해보세요! (준비운동, 순환운동, 스트레칭, 워밍업, 운동 전 스트레칭) [비온뒤 금쪽 운동 상담소] #9 (김수관 코치 &amp; 정진희 PD)</v>
+        <v>교실체육 전 3분 워밍업 (준비운동 | 스트레칭 | 교실 체력 트레이닝  )</v>
       </c>
       <c r="E31" t="str">
-        <v>zguPP2ymhH0</v>
+        <v>hMCvvDHB46o</v>
       </c>
       <c r="F31" t="str">
-        <v>16:48</v>
+        <v>03:07</v>
       </c>
       <c r="G31">
         <v>1050</v>
@@ -1779,19 +1894,19 @@
         <v>V0031</v>
       </c>
       <c r="B32" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C32" t="str">
-        <v>S41</v>
+        <v>S31</v>
       </c>
       <c r="D32" t="str">
-        <v>줄넘기 | 초등체육 | 온라인체육 | 줄넘기기초</v>
+        <v>[서초초등체육교실 시즌3] 준비운동</v>
       </c>
       <c r="E32" t="str">
-        <v>zPGci2cL6j4</v>
+        <v>ZmUj-E9A44E</v>
       </c>
       <c r="F32" t="str">
-        <v>05:14</v>
+        <v>04:43</v>
       </c>
       <c r="G32">
         <v>2021</v>
@@ -1808,19 +1923,19 @@
         <v>V0032</v>
       </c>
       <c r="B33" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C33" t="str">
-        <v>S41</v>
+        <v>S31</v>
       </c>
       <c r="D33" t="str">
-        <v>[1강]줄넘기 초보를 위한 줄넘기 기본 배우기!</v>
+        <v>온라인 체육 수업 - 5분 스트레칭 [준비운동]</v>
       </c>
       <c r="E33" t="str">
-        <v>Mdc7kmOKuMU</v>
+        <v>PFJe9i9UbZ4</v>
       </c>
       <c r="F33" t="str">
-        <v>04:31</v>
+        <v>05:09</v>
       </c>
       <c r="G33">
         <v>2992</v>
@@ -1837,19 +1952,19 @@
         <v>V0033</v>
       </c>
       <c r="B34" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C34" t="str">
-        <v>S41</v>
+        <v>S31</v>
       </c>
       <c r="D34" t="str">
-        <v>줄넘기처음배우기 초급강의 1부 / 줄넘기 잘하는법(온라인체육수업 ) 기초부터 탄탄하게</v>
+        <v>의자 앉아 맨손체조ㅣ책상 스트레칭ㅣ의자 스트레칭ㅣ교실 스트레칭ㅣ놀이 준비운동ㅣ쏭쌤TV</v>
       </c>
       <c r="E34" t="str">
-        <v>_yWerNDS2AQ</v>
+        <v>2lru6IsOQ6Y</v>
       </c>
       <c r="F34" t="str">
-        <v>06:58</v>
+        <v>04:05</v>
       </c>
       <c r="G34">
         <v>3963</v>
@@ -1866,19 +1981,19 @@
         <v>V0034</v>
       </c>
       <c r="B35" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C35" t="str">
-        <v>S41</v>
+        <v>S31</v>
       </c>
       <c r="D35" t="str">
-        <v>[양수쌤 놀이체육] 온라인 체육 - 줄넘기 양발 모아뛰기 2가지!</v>
+        <v>체육 수업 준비운동 및 정리운동 - 기백반 체육교실의 일상적인 준비운동 따라하기</v>
       </c>
       <c r="E35" t="str">
-        <v>nDvxGWOUNk4</v>
+        <v>erMfzZ5_or8</v>
       </c>
       <c r="F35" t="str">
-        <v>03:22</v>
+        <v>05:29</v>
       </c>
       <c r="G35">
         <v>4934</v>
@@ -1895,19 +2010,19 @@
         <v>V0035</v>
       </c>
       <c r="B36" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C36" t="str">
-        <v>S42</v>
+        <v>S31</v>
       </c>
       <c r="D36" t="str">
-        <v>[365+체육온활동] 초급 6. 혼자서 줄넘기</v>
+        <v>3분, 초간단 운동 전 워밍업 스트레칭(부상 예방, 운동효과 대박, 가동범위 증가)</v>
       </c>
       <c r="E36" t="str">
-        <v>XdQRqIR-x64</v>
+        <v>8qf727092l4</v>
       </c>
       <c r="F36" t="str">
-        <v>07:59</v>
+        <v>03:29</v>
       </c>
       <c r="G36">
         <v>5905</v>
@@ -1924,19 +2039,19 @@
         <v>V0036</v>
       </c>
       <c r="B37" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C37" t="str">
-        <v>S42</v>
+        <v>S31</v>
       </c>
       <c r="D37" t="str">
-        <v>제1강 줄넘기 기초과정</v>
+        <v>준비운동</v>
       </c>
       <c r="E37" t="str">
-        <v>P6RU0NUgu8E</v>
+        <v>_bqes3Cw5ug</v>
       </c>
       <c r="F37" t="str">
-        <v>08:46</v>
+        <v>03:27</v>
       </c>
       <c r="G37">
         <v>6876</v>
@@ -1953,19 +2068,19 @@
         <v>V0037</v>
       </c>
       <c r="B38" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C38" t="str">
-        <v>S42</v>
+        <v>S32</v>
       </c>
       <c r="D38" t="str">
-        <v>줄넘기 -기초과정</v>
+        <v>[마포구체육회]홈트레이닝/칼로리 폭파 4분 타바타</v>
       </c>
       <c r="E38" t="str">
-        <v>DnUmpP-_Chk</v>
+        <v>G9p1ZehAAnI</v>
       </c>
       <c r="F38" t="str">
-        <v>08:46</v>
+        <v>04:38</v>
       </c>
       <c r="G38">
         <v>7847</v>
@@ -1982,19 +2097,19 @@
         <v>V0038</v>
       </c>
       <c r="B39" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C39" t="str">
-        <v>S42</v>
+        <v>S32</v>
       </c>
       <c r="D39" t="str">
-        <v>줄넘기2(점프스쿼트)</v>
+        <v>체지방↓DOWN, 근력↑UP "4분 타바타 홈트레이닝" (초보자,중상급자 모두가능!)</v>
       </c>
       <c r="E39" t="str">
-        <v>zrPszwVKjJE</v>
+        <v>BL8kwdj-XWU</v>
       </c>
       <c r="F39" t="str">
-        <v>02:06</v>
+        <v>05:54</v>
       </c>
       <c r="G39">
         <v>8818</v>
@@ -2011,19 +2126,19 @@
         <v>V0039</v>
       </c>
       <c r="B40" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C40" t="str">
-        <v>S43</v>
+        <v>S32</v>
       </c>
       <c r="D40" t="str">
-        <v>줄넘기쌩쌩이 쉽게 하기[2단뛰기 연습방법]</v>
+        <v>집에서 누구나 [4분 타바타] 1편 / 화성시문화재단과 홈트레이닝하기</v>
       </c>
       <c r="E40" t="str">
-        <v>gT9Y9FBb1ic</v>
+        <v>RFFWIbUcBXo</v>
       </c>
       <c r="F40" t="str">
-        <v>01:22</v>
+        <v>10:42</v>
       </c>
       <c r="G40">
         <v>389</v>
@@ -2040,19 +2155,19 @@
         <v>V0040</v>
       </c>
       <c r="B41" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C41" t="str">
-        <v>S43</v>
+        <v>S32</v>
       </c>
       <c r="D41" t="str">
-        <v>2중뛰기/쌩쌩이/2단뛰기 뛰는 방법!!</v>
+        <v>운동초보에게 딱! 홈트 4분 타바타운동으로 저질체력 탈출해보자! | Low physical fitness? You can change it! Tabata for beginner</v>
       </c>
       <c r="E41" t="str">
-        <v>DwYFyXlwM40</v>
+        <v>BxElnlkcfts</v>
       </c>
       <c r="F41" t="str">
-        <v>04:19</v>
+        <v>04:35</v>
       </c>
       <c r="G41">
         <v>1360</v>
@@ -2069,19 +2184,19 @@
         <v>V0041</v>
       </c>
       <c r="B42" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C42" t="str">
-        <v>S43</v>
+        <v>S32</v>
       </c>
       <c r="D42" t="str">
-        <v>줄넘기 얼마나 아십니까? 줄넘기 2단뛰기 잘하는 법, 정말 천천히 알려드립니다 [ 달팽이레슨 ] 190716</v>
+        <v>[실전]하루 4분 체지방 태우기 운동 - 집에서 하는 다이어트 타바타 운동 5 [핏분 유쾌한 홈트레이닝]</v>
       </c>
       <c r="E42" t="str">
-        <v>G_jCU_oL8AE</v>
+        <v>ta-Uq_prRT8</v>
       </c>
       <c r="F42" t="str">
-        <v>05:08</v>
+        <v>06:34</v>
       </c>
       <c r="G42">
         <v>2331</v>
@@ -2098,19 +2213,19 @@
         <v>V0042</v>
       </c>
       <c r="B43" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C43" t="str">
-        <v>S43</v>
+        <v>S33</v>
       </c>
       <c r="D43" t="str">
-        <v>쌩쌩이, 2단뛰기 성공 하기 '2중뛰기' 하는 방법</v>
+        <v>뱃살 빼는 최고의 운동 ! 4분 쉬지 않고 (신 타바타 버전)ㅣ고민수</v>
       </c>
       <c r="E43" t="str">
-        <v>l9chx0Z7qBw</v>
+        <v>EPXeswXkJDg</v>
       </c>
       <c r="F43" t="str">
-        <v>02:02</v>
+        <v>06:27</v>
       </c>
       <c r="G43">
         <v>3302</v>
@@ -2127,19 +2242,19 @@
         <v>V0043</v>
       </c>
       <c r="B44" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C44" t="str">
-        <v>S44</v>
+        <v>S33</v>
       </c>
       <c r="D44" t="str">
-        <v>[8강]쌩쌩이 도전! 2단뛰기 마스터하기!</v>
+        <v>4분 운동으로 1시간 운동효과 ? 타바타 전신편 !/ 홈트레이닝</v>
       </c>
       <c r="E44" t="str">
-        <v>jmm8k9OmK1Y</v>
+        <v>4deNtH6p2U0</v>
       </c>
       <c r="F44" t="str">
-        <v>03:47</v>
+        <v>04:24</v>
       </c>
       <c r="G44">
         <v>4273</v>
@@ -2156,19 +2271,19 @@
         <v>V0044</v>
       </c>
       <c r="B45" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C45" t="str">
-        <v>S44</v>
+        <v>S33</v>
       </c>
       <c r="D45" t="str">
-        <v>2분 안에 배우는 줄넘기 기본동작 - 2중뛰기(=쌩쌩이) (feat.점프스쿨)</v>
+        <v>Day35 하루 4분 홈트 타바타운동(8가지 코어 등척성운동 )</v>
       </c>
       <c r="E45" t="str">
-        <v>XA3xY1WCvn8</v>
+        <v>esPoIcFC_T4</v>
       </c>
       <c r="F45" t="str">
-        <v>01:27</v>
+        <v>06:08</v>
       </c>
       <c r="G45">
         <v>5244</v>
@@ -2185,19 +2300,19 @@
         <v>V0045</v>
       </c>
       <c r="B46" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C46" t="str">
-        <v>S45</v>
+        <v>S34</v>
       </c>
       <c r="D46" t="str">
-        <v>줄넘기 중수에서 고수로! 뒤로 줄넘기+쌩쌩이ㅣ이현준의 명징티비 이카이스 마이풀</v>
+        <v>쳐진 엉덩이 올리는 4분 타바타 운동 (홈트레이닝)ㅣ고민수</v>
       </c>
       <c r="E46" t="str">
-        <v>adt2JguLrAo</v>
+        <v>AytACfar2AI</v>
       </c>
       <c r="F46" t="str">
-        <v>02:40</v>
+        <v>09:18</v>
       </c>
       <c r="G46">
         <v>6215</v>
@@ -2214,19 +2329,19 @@
         <v>V0046</v>
       </c>
       <c r="B47" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C47" t="str">
-        <v>S45</v>
+        <v>S34</v>
       </c>
       <c r="D47" t="str">
-        <v>줄넘기,2단뛰기,100개</v>
+        <v>[주원홈트] 준비운동 스트레칭 - 운동 전에는 꼭 따라해야 하는 워밍업 영상</v>
       </c>
       <c r="E47" t="str">
-        <v>i6gF_5J4fek</v>
+        <v>2oN6SFl85VY</v>
       </c>
       <c r="F47" t="str">
-        <v>01:02</v>
+        <v>06:24</v>
       </c>
       <c r="G47">
         <v>7186</v>
@@ -2243,19 +2358,19 @@
         <v>V0047</v>
       </c>
       <c r="B48" t="str">
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="C48" t="str">
-        <v>S46</v>
+        <v>S34</v>
       </c>
       <c r="D48" t="str">
-        <v>(고화질) 초등 줄넘기 공인급수 10~1급 풀영상! (Jump rope)</v>
+        <v>하루를 이 동작으로 시작해보세요! (준비운동, 순환운동, 스트레칭, 워밍업, 운동 전 스트레칭) [비온뒤 금쪽 운동 상담소] #9 (김수관 코치 &amp; 정진희 PD)</v>
       </c>
       <c r="E48" t="str">
-        <v>HHmor6wmxMo</v>
+        <v>zguPP2ymhH0</v>
       </c>
       <c r="F48" t="str">
-        <v>09:42</v>
+        <v>16:48</v>
       </c>
       <c r="G48">
         <v>8157</v>
@@ -2272,19 +2387,19 @@
         <v>V0048</v>
       </c>
       <c r="B49" t="str">
-        <v>C5</v>
+        <v>C3</v>
       </c>
       <c r="C49" t="str">
-        <v>S51</v>
+        <v>S35</v>
       </c>
       <c r="D49" t="str">
-        <v>★튼튼쌤의 율동체조교실 인기율동 특집★ㅣ핑크퐁 인기 율동동요와 함께 하는 신나는 댄스♬ㅣ곰 세마리, 멋쟁이 토마토, 악어 떼, 작은 주전자, 주먹 쥐고ㅣ핑크퐁! 인기동요</v>
+        <v>[Cool-Down] 마무리 스트레칭 누워서 하는 정리운동 탄력에 필수!!</v>
       </c>
       <c r="E49" t="str">
-        <v>dw31Gdfj7oY</v>
+        <v>d3MtqJSDO90</v>
       </c>
       <c r="F49" t="str">
-        <v>11:40</v>
+        <v>10:11</v>
       </c>
       <c r="G49">
         <v>9128</v>
@@ -2301,19 +2416,19 @@
         <v>V0049</v>
       </c>
       <c r="B50" t="str">
-        <v>C5</v>
+        <v>C3</v>
       </c>
       <c r="C50" t="str">
-        <v>S51</v>
+        <v>S35</v>
       </c>
       <c r="D50" t="str">
-        <v>체조 노래모음ㅣ인기동요모음ㅣ친구와 즐거운 노래와 댄스로 신나게 체조 율동을 즐겨보아요!ㅣ랄라라키즈</v>
+        <v>운동 후, 쿨다운 스트레칭 10분 꼭 해주세요 (정리운동 스트레칭, 운동후 근육통 풀기)</v>
       </c>
       <c r="E50" t="str">
-        <v>FiVBh8pv78Y</v>
+        <v>X8t6C07BJ80</v>
       </c>
       <c r="F50" t="str">
-        <v>03:22</v>
+        <v>10:06</v>
       </c>
       <c r="G50">
         <v>699</v>
@@ -2330,19 +2445,19 @@
         <v>V0050</v>
       </c>
       <c r="B51" t="str">
-        <v>C5</v>
+        <v>C3</v>
       </c>
       <c r="C51" t="str">
-        <v>S51</v>
+        <v>S35</v>
       </c>
       <c r="D51" t="str">
-        <v>높이높이 쭉쭉 ♪ | 신나는 율동 체조 | 응급처치 프린세스와 함께 쭉쭉 체조해요! | 율동동요 | 어린이 인기동요★지니키즈</v>
+        <v>5분만에 끝나는, 달리기 후 스트레칭, #쿨다운 #마무리운동</v>
       </c>
       <c r="E51" t="str">
-        <v>OP8fuogWSlQ</v>
+        <v>mdvTr_xhiH8</v>
       </c>
       <c r="F51" t="str">
-        <v>00:58</v>
+        <v>07:39</v>
       </c>
       <c r="G51">
         <v>1670</v>
@@ -2359,19 +2474,19 @@
         <v>V0051</v>
       </c>
       <c r="B52" t="str">
-        <v>C5</v>
+        <v>C3</v>
       </c>
       <c r="C52" t="str">
-        <v>S51</v>
+        <v>S35</v>
       </c>
       <c r="D52" t="str">
-        <v>쭉쭉 체조 🎶 | 신나는 댄스타임 | 어린이 율동 | 인기율동 | 어린이 홈트 | 로티프렌즈 인기동요 | LOTTY FRIENDS</v>
+        <v>하루 6분 운동 후 마무리 쿨다운 스트레칭 (전신 스트레칭)</v>
       </c>
       <c r="E52" t="str">
-        <v>mfpamFUdivE</v>
+        <v>9GawCESbFFk</v>
       </c>
       <c r="F52" t="str">
-        <v>03:22</v>
+        <v>06:29</v>
       </c>
       <c r="G52">
         <v>2641</v>
@@ -2388,19 +2503,19 @@
         <v>V0052</v>
       </c>
       <c r="B53" t="str">
-        <v>C5</v>
+        <v>C3</v>
       </c>
       <c r="C53" t="str">
-        <v>S52</v>
+        <v>S35</v>
       </c>
       <c r="D53" t="str">
-        <v>신나는 율동동요 댄스 모음 60분 ♪ | 시원하게 몸을 움직여요🤸‍♂️| 동물동요 l 방귀체조 | 어린이 인기동요 연속듣기 ★ 지니키즈</v>
+        <v>운동후 스트레칭 모음,  이거 하나면 운동효과 2배! 쿨다운 끝!</v>
       </c>
       <c r="E53" t="str">
-        <v>_EkTLdKEOy4</v>
+        <v>4TwQwVFLi4Q</v>
       </c>
       <c r="F53" t="str">
-        <v>48:34</v>
+        <v>07:55</v>
       </c>
       <c r="G53">
         <v>3612</v>
@@ -2417,19 +2532,19 @@
         <v>V0053</v>
       </c>
       <c r="B54" t="str">
-        <v>C5</v>
+        <v>C3</v>
       </c>
       <c r="C54" t="str">
-        <v>S52</v>
+        <v>S35</v>
       </c>
       <c r="D54" t="str">
-        <v>뚝딱뚝딱 율동 동요! 💃 | 신나게 몸을 움직여요 | 어린이를 위한 운동 노래</v>
+        <v>홈트레이닝 마무리 운동-웃음체조 정리운동 스트레칭버전 집에서따라하기</v>
       </c>
       <c r="E54" t="str">
-        <v>DFT4-ro_iIM</v>
+        <v>YXzPcEATOPg</v>
       </c>
       <c r="F54" t="str">
-        <v>15:49</v>
+        <v>04:20</v>
       </c>
       <c r="G54">
         <v>4583</v>
@@ -2446,19 +2561,19 @@
         <v>V0054</v>
       </c>
       <c r="B55" t="str">
-        <v>C5</v>
+        <v>C3</v>
       </c>
       <c r="C55" t="str">
-        <v>S52</v>
+        <v>S36</v>
       </c>
       <c r="D55" t="str">
-        <v>오늘도 튼튼하게💪🏻튼튼쌤과 체조해요! | 인기 체조 모음집 | 몽키 바나나, 아기상어 체조, 쑥쑥 키크기 체조 | 신나는 율동 체조 | 어린이 체조 | 핑크퐁! 인기동요</v>
+        <v>교실놀이로 레크레이션 진행해보기-재미있는 놀이 게임 레크리에이션</v>
       </c>
       <c r="E55" t="str">
-        <v>5Hll_yymS2w</v>
+        <v>z149ha1sCbQ</v>
       </c>
       <c r="F55" t="str">
-        <v>1:30:16</v>
+        <v>07:50</v>
       </c>
       <c r="G55">
         <v>5554</v>
@@ -2475,19 +2590,19 @@
         <v>V0055</v>
       </c>
       <c r="B56" t="str">
-        <v>C6</v>
+        <v>C3</v>
       </c>
       <c r="C56" t="str">
-        <v>S61</v>
+        <v>S36</v>
       </c>
       <c r="D56" t="str">
-        <v>국기 퀴즈 | 국기 맞히기 195개 | 3초 안에 국기 맞히기 | 국기 100+ 도전 🌏 | flag quiz 2024</v>
+        <v>놀이게임 5가지-초등 놀이 레크레이션 신나는 야외놀이 강당놀이 교실놀이</v>
       </c>
       <c r="E56" t="str">
-        <v>Ln9mCebyeNk</v>
+        <v>Gr9qZrju9Pk</v>
       </c>
       <c r="F56" t="str">
-        <v>18:19</v>
+        <v>12:18</v>
       </c>
       <c r="G56">
         <v>6525</v>
@@ -2504,19 +2619,19 @@
         <v>V0056</v>
       </c>
       <c r="B57" t="str">
-        <v>C6</v>
+        <v>C3</v>
       </c>
       <c r="C57" t="str">
-        <v>S61</v>
+        <v>S36</v>
       </c>
       <c r="D57" t="str">
-        <v>세계여러나라 국기퀴즈 | 국기맞추기 게임 | 세계여러나라 국기 | 세계여러나라 놀이 | 세계여러나라 퀴즈 (어린이 / 유아 / 초등저학년)</v>
+        <v>교실체육 | 경쟁 없는 놀이! 초간단 원형 놀이 3종 세트!</v>
       </c>
       <c r="E57" t="str">
-        <v>f9PuBMgLtpA</v>
+        <v>36Gc0L7X-_M</v>
       </c>
       <c r="F57" t="str">
-        <v>03:43</v>
+        <v>04:56</v>
       </c>
       <c r="G57">
         <v>7496</v>
@@ -2533,19 +2648,19 @@
         <v>V0057</v>
       </c>
       <c r="B58" t="str">
-        <v>C6</v>
+        <v>C3</v>
       </c>
       <c r="C58" t="str">
-        <v>S61</v>
+        <v>S36</v>
       </c>
       <c r="D58" t="str">
-        <v>🚩최고 난이도 국기 보고  56개국 나라 이름 맞추기 8단계 퀴즈.</v>
+        <v>교실놀이ㅣ책상을 활용한 13종 교실놀이 설명ㅣ놀이체육ㅣ초등체육</v>
       </c>
       <c r="E58" t="str">
-        <v>L73dXfVsLKc</v>
+        <v>mOHgNUGpZLE</v>
       </c>
       <c r="F58" t="str">
-        <v>09:28</v>
+        <v>11:43</v>
       </c>
       <c r="G58">
         <v>8467</v>
@@ -2562,19 +2677,19 @@
         <v>V0058</v>
       </c>
       <c r="B59" t="str">
-        <v>C6</v>
+        <v>C3</v>
       </c>
       <c r="C59" t="str">
-        <v>S61</v>
+        <v>S36</v>
       </c>
       <c r="D59" t="str">
-        <v>국기 맞히기 퀴즈, 국기 사진 보고 100개 나라 맞히기, 난이도 초중급</v>
+        <v>[교실놀이]  "준비물 없이 즐기는 재미있는 실내놀이 전편  풀영상"  |팍찐놀이| 레크리에이션|</v>
       </c>
       <c r="E59" t="str">
-        <v>D8vF6CXRhgc</v>
+        <v>gYQhS1ioY0o</v>
       </c>
       <c r="F59" t="str">
-        <v>13:41</v>
+        <v>1:02:43</v>
       </c>
       <c r="G59">
         <v>9438</v>
@@ -2591,19 +2706,19 @@
         <v>V0059</v>
       </c>
       <c r="B60" t="str">
-        <v>C6</v>
+        <v>C3</v>
       </c>
       <c r="C60" t="str">
-        <v>S62</v>
+        <v>S36</v>
       </c>
       <c r="D60" t="str">
-        <v>집중력 향상 놀이! "안 숨은그림 찾기 1탄"</v>
+        <v>원바운딩놀이! 협력놀이! 교실놀이체육!  실내체육! 놀이! 초등체육! fun p.e. games! Physical Education!</v>
       </c>
       <c r="E60" t="str">
-        <v>nA9I1iv_E8w</v>
+        <v>juCbUO6zpL0</v>
       </c>
       <c r="F60" t="str">
-        <v>06:46</v>
+        <v>02:11</v>
       </c>
       <c r="G60">
         <v>1009</v>
@@ -2615,9 +2730,1314 @@
         <v>Y</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>V0060</v>
+      </c>
+      <c r="B61" t="str">
+        <v>C3</v>
+      </c>
+      <c r="C61" t="str">
+        <v>S36</v>
+      </c>
+      <c r="D61" t="str">
+        <v>교실놀이 ㅣ 새학기 교실놀이 5종세트</v>
+      </c>
+      <c r="E61" t="str">
+        <v>A2X7o51KwuI</v>
+      </c>
+      <c r="F61" t="str">
+        <v>06:54</v>
+      </c>
+      <c r="G61">
+        <v>1980</v>
+      </c>
+      <c r="H61" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>V0061</v>
+      </c>
+      <c r="B62" t="str">
+        <v>C3</v>
+      </c>
+      <c r="C62" t="str">
+        <v>S36</v>
+      </c>
+      <c r="D62" t="str">
+        <v>교실놀이 ㅣ 오른쪽! 왼쪽! 흔들어~~ ㅣ 레크레이션</v>
+      </c>
+      <c r="E62" t="str">
+        <v>gBsXje_teyg</v>
+      </c>
+      <c r="F62" t="str">
+        <v>01:24</v>
+      </c>
+      <c r="G62">
+        <v>2951</v>
+      </c>
+      <c r="H62" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I62" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>V0062</v>
+      </c>
+      <c r="B63" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C63" t="str">
+        <v>S41</v>
+      </c>
+      <c r="D63" t="str">
+        <v>줄넘기 | 초등체육 | 온라인체육 | 줄넘기기초</v>
+      </c>
+      <c r="E63" t="str">
+        <v>zPGci2cL6j4</v>
+      </c>
+      <c r="F63" t="str">
+        <v>05:14</v>
+      </c>
+      <c r="G63">
+        <v>3922</v>
+      </c>
+      <c r="H63" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>V0063</v>
+      </c>
+      <c r="B64" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C64" t="str">
+        <v>S41</v>
+      </c>
+      <c r="D64" t="str">
+        <v>[1강]줄넘기 초보를 위한 줄넘기 기본 배우기!</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Mdc7kmOKuMU</v>
+      </c>
+      <c r="F64" t="str">
+        <v>04:31</v>
+      </c>
+      <c r="G64">
+        <v>4893</v>
+      </c>
+      <c r="H64" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I64" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>V0064</v>
+      </c>
+      <c r="B65" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C65" t="str">
+        <v>S41</v>
+      </c>
+      <c r="D65" t="str">
+        <v>줄넘기처음배우기 초급강의 1부 / 줄넘기 잘하는법(온라인체육수업 ) 기초부터 탄탄하게</v>
+      </c>
+      <c r="E65" t="str">
+        <v>_yWerNDS2AQ</v>
+      </c>
+      <c r="F65" t="str">
+        <v>06:58</v>
+      </c>
+      <c r="G65">
+        <v>5864</v>
+      </c>
+      <c r="H65" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I65" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>V0065</v>
+      </c>
+      <c r="B66" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C66" t="str">
+        <v>S41</v>
+      </c>
+      <c r="D66" t="str">
+        <v>[양수쌤 놀이체육] 온라인 체육 - 줄넘기 양발 모아뛰기 2가지!</v>
+      </c>
+      <c r="E66" t="str">
+        <v>nDvxGWOUNk4</v>
+      </c>
+      <c r="F66" t="str">
+        <v>03:22</v>
+      </c>
+      <c r="G66">
+        <v>6835</v>
+      </c>
+      <c r="H66" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>V0066</v>
+      </c>
+      <c r="B67" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C67" t="str">
+        <v>S42</v>
+      </c>
+      <c r="D67" t="str">
+        <v>[365+체육온활동] 초급 6. 혼자서 줄넘기</v>
+      </c>
+      <c r="E67" t="str">
+        <v>XdQRqIR-x64</v>
+      </c>
+      <c r="F67" t="str">
+        <v>07:59</v>
+      </c>
+      <c r="G67">
+        <v>7806</v>
+      </c>
+      <c r="H67" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I67" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>V0067</v>
+      </c>
+      <c r="B68" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C68" t="str">
+        <v>S42</v>
+      </c>
+      <c r="D68" t="str">
+        <v>제1강 줄넘기 기초과정</v>
+      </c>
+      <c r="E68" t="str">
+        <v>P6RU0NUgu8E</v>
+      </c>
+      <c r="F68" t="str">
+        <v>08:46</v>
+      </c>
+      <c r="G68">
+        <v>8777</v>
+      </c>
+      <c r="H68" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I68" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>V0068</v>
+      </c>
+      <c r="B69" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C69" t="str">
+        <v>S42</v>
+      </c>
+      <c r="D69" t="str">
+        <v>줄넘기 -기초과정</v>
+      </c>
+      <c r="E69" t="str">
+        <v>DnUmpP-_Chk</v>
+      </c>
+      <c r="F69" t="str">
+        <v>08:46</v>
+      </c>
+      <c r="G69">
+        <v>348</v>
+      </c>
+      <c r="H69" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I69" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>V0069</v>
+      </c>
+      <c r="B70" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C70" t="str">
+        <v>S42</v>
+      </c>
+      <c r="D70" t="str">
+        <v>줄넘기2(점프스쿼트)</v>
+      </c>
+      <c r="E70" t="str">
+        <v>zrPszwVKjJE</v>
+      </c>
+      <c r="F70" t="str">
+        <v>02:06</v>
+      </c>
+      <c r="G70">
+        <v>1319</v>
+      </c>
+      <c r="H70" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I70" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>V0070</v>
+      </c>
+      <c r="B71" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C71" t="str">
+        <v>S43</v>
+      </c>
+      <c r="D71" t="str">
+        <v>줄넘기쌩쌩이 쉽게 하기[2단뛰기 연습방법]</v>
+      </c>
+      <c r="E71" t="str">
+        <v>gT9Y9FBb1ic</v>
+      </c>
+      <c r="F71" t="str">
+        <v>01:22</v>
+      </c>
+      <c r="G71">
+        <v>2290</v>
+      </c>
+      <c r="H71" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I71" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>V0071</v>
+      </c>
+      <c r="B72" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C72" t="str">
+        <v>S43</v>
+      </c>
+      <c r="D72" t="str">
+        <v>2중뛰기/쌩쌩이/2단뛰기 뛰는 방법!!</v>
+      </c>
+      <c r="E72" t="str">
+        <v>DwYFyXlwM40</v>
+      </c>
+      <c r="F72" t="str">
+        <v>04:19</v>
+      </c>
+      <c r="G72">
+        <v>3261</v>
+      </c>
+      <c r="H72" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I72" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>V0072</v>
+      </c>
+      <c r="B73" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C73" t="str">
+        <v>S43</v>
+      </c>
+      <c r="D73" t="str">
+        <v>줄넘기 얼마나 아십니까? 줄넘기 2단뛰기 잘하는 법, 정말 천천히 알려드립니다 [ 달팽이레슨 ] 190716</v>
+      </c>
+      <c r="E73" t="str">
+        <v>G_jCU_oL8AE</v>
+      </c>
+      <c r="F73" t="str">
+        <v>05:08</v>
+      </c>
+      <c r="G73">
+        <v>4232</v>
+      </c>
+      <c r="H73" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I73" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>V0073</v>
+      </c>
+      <c r="B74" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C74" t="str">
+        <v>S43</v>
+      </c>
+      <c r="D74" t="str">
+        <v>쌩쌩이, 2단뛰기 성공 하기 '2중뛰기' 하는 방법</v>
+      </c>
+      <c r="E74" t="str">
+        <v>l9chx0Z7qBw</v>
+      </c>
+      <c r="F74" t="str">
+        <v>02:02</v>
+      </c>
+      <c r="G74">
+        <v>5203</v>
+      </c>
+      <c r="H74" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I74" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>V0074</v>
+      </c>
+      <c r="B75" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C75" t="str">
+        <v>S44</v>
+      </c>
+      <c r="D75" t="str">
+        <v>[8강]쌩쌩이 도전! 2단뛰기 마스터하기!</v>
+      </c>
+      <c r="E75" t="str">
+        <v>jmm8k9OmK1Y</v>
+      </c>
+      <c r="F75" t="str">
+        <v>03:47</v>
+      </c>
+      <c r="G75">
+        <v>6174</v>
+      </c>
+      <c r="H75" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I75" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>V0075</v>
+      </c>
+      <c r="B76" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C76" t="str">
+        <v>S44</v>
+      </c>
+      <c r="D76" t="str">
+        <v>2분 안에 배우는 줄넘기 기본동작 - 2중뛰기(=쌩쌩이) (feat.점프스쿨)</v>
+      </c>
+      <c r="E76" t="str">
+        <v>XA3xY1WCvn8</v>
+      </c>
+      <c r="F76" t="str">
+        <v>01:27</v>
+      </c>
+      <c r="G76">
+        <v>7145</v>
+      </c>
+      <c r="H76" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I76" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>V0076</v>
+      </c>
+      <c r="B77" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C77" t="str">
+        <v>S44</v>
+      </c>
+      <c r="D77" t="str">
+        <v>줄넘기 중수에서 고수로! 뒤로 줄넘기+쌩쌩이ㅣ이현준의 명징티비 이카이스 마이풀</v>
+      </c>
+      <c r="E77" t="str">
+        <v>adt2JguLrAo</v>
+      </c>
+      <c r="F77" t="str">
+        <v>02:40</v>
+      </c>
+      <c r="G77">
+        <v>8116</v>
+      </c>
+      <c r="H77" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I77" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>V0077</v>
+      </c>
+      <c r="B78" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C78" t="str">
+        <v>S44</v>
+      </c>
+      <c r="D78" t="str">
+        <v>줄넘기,2단뛰기,100개</v>
+      </c>
+      <c r="E78" t="str">
+        <v>i6gF_5J4fek</v>
+      </c>
+      <c r="F78" t="str">
+        <v>01:02</v>
+      </c>
+      <c r="G78">
+        <v>9087</v>
+      </c>
+      <c r="H78" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I78" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>V0078</v>
+      </c>
+      <c r="B79" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C79" t="str">
+        <v>S45</v>
+      </c>
+      <c r="D79" t="str">
+        <v>[윤쌤의 신나는 음악줄넘기] 초급 1단계 기본 동작</v>
+      </c>
+      <c r="E79" t="str">
+        <v>-hDMjJr9Smc</v>
+      </c>
+      <c r="F79" t="str">
+        <v>02:03</v>
+      </c>
+      <c r="G79">
+        <v>658</v>
+      </c>
+      <c r="H79" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I79" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>V0079</v>
+      </c>
+      <c r="B80" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C80" t="str">
+        <v>S45</v>
+      </c>
+      <c r="D80" t="str">
+        <v>[윤쌤의 신나는 음악줄넘기] 고급 1단계 기본 동작</v>
+      </c>
+      <c r="E80" t="str">
+        <v>aYRIfdsH0u8</v>
+      </c>
+      <c r="F80" t="str">
+        <v>01:59</v>
+      </c>
+      <c r="G80">
+        <v>1629</v>
+      </c>
+      <c r="H80" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I80" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>V0080</v>
+      </c>
+      <c r="B81" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C81" t="str">
+        <v>S45</v>
+      </c>
+      <c r="D81" t="str">
+        <v>방학특집! 신나는 음악과 함께 즐기는 줄넘기 기본동작 7가지!🌈🎶</v>
+      </c>
+      <c r="E81" t="str">
+        <v>SNC04hlGt6Y</v>
+      </c>
+      <c r="F81" t="str">
+        <v>03:46</v>
+      </c>
+      <c r="G81">
+        <v>2600</v>
+      </c>
+      <c r="H81" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I81" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>V0081</v>
+      </c>
+      <c r="B82" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C82" t="str">
+        <v>S45</v>
+      </c>
+      <c r="D82" t="str">
+        <v>초보자도 OK! 인기동요 네잎클로버와 함께 즐기는 음악줄넘기🍀🎶</v>
+      </c>
+      <c r="E82" t="str">
+        <v>23hTV_VXKNE</v>
+      </c>
+      <c r="F82" t="str">
+        <v>01:18</v>
+      </c>
+      <c r="G82">
+        <v>3571</v>
+      </c>
+      <c r="H82" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I82" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>V0082</v>
+      </c>
+      <c r="B83" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C83" t="str">
+        <v>S45</v>
+      </c>
+      <c r="D83" t="str">
+        <v>[음악줄넘기]초등학교 2학년 넘사벽 줄넘기 | 줄넘기 실력을 뽐내는 초등학생 | Jump Rope</v>
+      </c>
+      <c r="E83" t="str">
+        <v>6PvI3f7jZfE</v>
+      </c>
+      <c r="F83" t="str">
+        <v>01:06</v>
+      </c>
+      <c r="G83">
+        <v>4542</v>
+      </c>
+      <c r="H83" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I83" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>V0083</v>
+      </c>
+      <c r="B84" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C84" t="str">
+        <v>S45</v>
+      </c>
+      <c r="D84" t="str">
+        <v>줄넘기시범공연</v>
+      </c>
+      <c r="E84" t="str">
+        <v>wWEsWFTJCnk</v>
+      </c>
+      <c r="F84" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="G84">
+        <v>5513</v>
+      </c>
+      <c r="H84" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>V0084</v>
+      </c>
+      <c r="B85" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C85" t="str">
+        <v>S46</v>
+      </c>
+      <c r="D85" t="str">
+        <v>(고화질) 초등 줄넘기 공인급수 10~1급 풀영상! (Jump rope)</v>
+      </c>
+      <c r="E85" t="str">
+        <v>HHmor6wmxMo</v>
+      </c>
+      <c r="F85" t="str">
+        <v>09:42</v>
+      </c>
+      <c r="G85">
+        <v>6484</v>
+      </c>
+      <c r="H85" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I85" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>V0085</v>
+      </c>
+      <c r="B86" t="str">
+        <v>C5</v>
+      </c>
+      <c r="C86" t="str">
+        <v>S51</v>
+      </c>
+      <c r="D86" t="str">
+        <v>★튼튼쌤의 율동체조교실 인기율동 특집★ㅣ핑크퐁 인기 율동동요와 함께 하는 신나는 댄스♬ㅣ곰 세마리, 멋쟁이 토마토, 악어 떼, 작은 주전자, 주먹 쥐고ㅣ핑크퐁! 인기동요</v>
+      </c>
+      <c r="E86" t="str">
+        <v>dw31Gdfj7oY</v>
+      </c>
+      <c r="F86" t="str">
+        <v>11:40</v>
+      </c>
+      <c r="G86">
+        <v>7455</v>
+      </c>
+      <c r="H86" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I86" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>V0086</v>
+      </c>
+      <c r="B87" t="str">
+        <v>C5</v>
+      </c>
+      <c r="C87" t="str">
+        <v>S51</v>
+      </c>
+      <c r="D87" t="str">
+        <v>체조 노래모음ㅣ인기동요모음ㅣ친구와 즐거운 노래와 댄스로 신나게 체조 율동을 즐겨보아요!ㅣ랄라라키즈</v>
+      </c>
+      <c r="E87" t="str">
+        <v>FiVBh8pv78Y</v>
+      </c>
+      <c r="F87" t="str">
+        <v>03:22</v>
+      </c>
+      <c r="G87">
+        <v>8426</v>
+      </c>
+      <c r="H87" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I87" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>V0087</v>
+      </c>
+      <c r="B88" t="str">
+        <v>C5</v>
+      </c>
+      <c r="C88" t="str">
+        <v>S51</v>
+      </c>
+      <c r="D88" t="str">
+        <v>높이높이 쭉쭉 ♪ | 신나는 율동 체조 | 응급처치 프린세스와 함께 쭉쭉 체조해요! | 율동동요 | 어린이 인기동요★지니키즈</v>
+      </c>
+      <c r="E88" t="str">
+        <v>OP8fuogWSlQ</v>
+      </c>
+      <c r="F88" t="str">
+        <v>00:58</v>
+      </c>
+      <c r="G88">
+        <v>9397</v>
+      </c>
+      <c r="H88" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I88" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>V0088</v>
+      </c>
+      <c r="B89" t="str">
+        <v>C5</v>
+      </c>
+      <c r="C89" t="str">
+        <v>S51</v>
+      </c>
+      <c r="D89" t="str">
+        <v>쭉쭉 체조 🎶 | 신나는 댄스타임 | 어린이 율동 | 인기율동 | 어린이 홈트 | 로티프렌즈 인기동요 | LOTTY FRIENDS</v>
+      </c>
+      <c r="E89" t="str">
+        <v>mfpamFUdivE</v>
+      </c>
+      <c r="F89" t="str">
+        <v>03:22</v>
+      </c>
+      <c r="G89">
+        <v>968</v>
+      </c>
+      <c r="H89" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I89" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>V0089</v>
+      </c>
+      <c r="B90" t="str">
+        <v>C5</v>
+      </c>
+      <c r="C90" t="str">
+        <v>S52</v>
+      </c>
+      <c r="D90" t="str">
+        <v>신나는 율동동요 댄스 모음 60분 ♪ | 시원하게 몸을 움직여요🤸‍♂️| 동물동요 l 방귀체조 | 어린이 인기동요 연속듣기 ★ 지니키즈</v>
+      </c>
+      <c r="E90" t="str">
+        <v>_EkTLdKEOy4</v>
+      </c>
+      <c r="F90" t="str">
+        <v>48:34</v>
+      </c>
+      <c r="G90">
+        <v>1939</v>
+      </c>
+      <c r="H90" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I90" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>V0090</v>
+      </c>
+      <c r="B91" t="str">
+        <v>C5</v>
+      </c>
+      <c r="C91" t="str">
+        <v>S52</v>
+      </c>
+      <c r="D91" t="str">
+        <v>뚝딱뚝딱 율동 동요! 💃 | 신나게 몸을 움직여요 | 어린이를 위한 운동 노래</v>
+      </c>
+      <c r="E91" t="str">
+        <v>DFT4-ro_iIM</v>
+      </c>
+      <c r="F91" t="str">
+        <v>15:49</v>
+      </c>
+      <c r="G91">
+        <v>2910</v>
+      </c>
+      <c r="H91" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I91" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>V0091</v>
+      </c>
+      <c r="B92" t="str">
+        <v>C5</v>
+      </c>
+      <c r="C92" t="str">
+        <v>S52</v>
+      </c>
+      <c r="D92" t="str">
+        <v>오늘도 튼튼하게💪🏻튼튼쌤과 체조해요! | 인기 체조 모음집 | 몽키 바나나, 아기상어 체조, 쑥쑥 키크기 체조 | 신나는 율동 체조 | 어린이 체조 | 핑크퐁! 인기동요</v>
+      </c>
+      <c r="E92" t="str">
+        <v>5Hll_yymS2w</v>
+      </c>
+      <c r="F92" t="str">
+        <v>1:30:16</v>
+      </c>
+      <c r="G92">
+        <v>3881</v>
+      </c>
+      <c r="H92" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I92" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>V0092</v>
+      </c>
+      <c r="B93" t="str">
+        <v>C5</v>
+      </c>
+      <c r="C93" t="str">
+        <v>S53</v>
+      </c>
+      <c r="D93" t="str">
+        <v>🕺 SODA POP - Saja Boys 간단춤 | 따라하기 쉬운 K-POP 안무 | 케데몬 | 흥딩스쿨</v>
+      </c>
+      <c r="E93" t="str">
+        <v>GKkixovHHro</v>
+      </c>
+      <c r="F93" t="str">
+        <v>01:41</v>
+      </c>
+      <c r="G93">
+        <v>4852</v>
+      </c>
+      <c r="H93" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I93" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>V0093</v>
+      </c>
+      <c r="B94" t="str">
+        <v>C5</v>
+      </c>
+      <c r="C94" t="str">
+        <v>S53</v>
+      </c>
+      <c r="D94" t="str">
+        <v>키즈 댄스 k-pop 안무 기초 배우기 | 캐리tv 히트송-‘럽럽(Love Love)’ 안무 기본기 배우기 part.2 | k-pop Kids dance class</v>
+      </c>
+      <c r="E94" t="str">
+        <v>YDFWIe-ibz8</v>
+      </c>
+      <c r="F94" t="str">
+        <v>05:48</v>
+      </c>
+      <c r="G94">
+        <v>5823</v>
+      </c>
+      <c r="H94" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I94" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>V0094</v>
+      </c>
+      <c r="B95" t="str">
+        <v>C6</v>
+      </c>
+      <c r="C95" t="str">
+        <v>S61</v>
+      </c>
+      <c r="D95" t="str">
+        <v>국기 퀴즈 | 국기 맞히기 195개 | 3초 안에 국기 맞히기 | 국기 100+ 도전 🌏 | flag quiz 2024</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Ln9mCebyeNk</v>
+      </c>
+      <c r="F95" t="str">
+        <v>18:19</v>
+      </c>
+      <c r="G95">
+        <v>6794</v>
+      </c>
+      <c r="H95" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I95" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>V0095</v>
+      </c>
+      <c r="B96" t="str">
+        <v>C6</v>
+      </c>
+      <c r="C96" t="str">
+        <v>S61</v>
+      </c>
+      <c r="D96" t="str">
+        <v>세계여러나라 국기퀴즈 | 국기맞추기 게임 | 세계여러나라 국기 | 세계여러나라 놀이 | 세계여러나라 퀴즈 (어린이 / 유아 / 초등저학년)</v>
+      </c>
+      <c r="E96" t="str">
+        <v>f9PuBMgLtpA</v>
+      </c>
+      <c r="F96" t="str">
+        <v>03:43</v>
+      </c>
+      <c r="G96">
+        <v>7765</v>
+      </c>
+      <c r="H96" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I96" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>V0096</v>
+      </c>
+      <c r="B97" t="str">
+        <v>C6</v>
+      </c>
+      <c r="C97" t="str">
+        <v>S61</v>
+      </c>
+      <c r="D97" t="str">
+        <v>🚩최고 난이도 국기 보고  56개국 나라 이름 맞추기 8단계 퀴즈.</v>
+      </c>
+      <c r="E97" t="str">
+        <v>L73dXfVsLKc</v>
+      </c>
+      <c r="F97" t="str">
+        <v>09:28</v>
+      </c>
+      <c r="G97">
+        <v>8736</v>
+      </c>
+      <c r="H97" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I97" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>V0097</v>
+      </c>
+      <c r="B98" t="str">
+        <v>C6</v>
+      </c>
+      <c r="C98" t="str">
+        <v>S61</v>
+      </c>
+      <c r="D98" t="str">
+        <v>국기 맞히기 퀴즈, 국기 사진 보고 100개 나라 맞히기, 난이도 초중급</v>
+      </c>
+      <c r="E98" t="str">
+        <v>D8vF6CXRhgc</v>
+      </c>
+      <c r="F98" t="str">
+        <v>13:41</v>
+      </c>
+      <c r="G98">
+        <v>307</v>
+      </c>
+      <c r="H98" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I98" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>V0098</v>
+      </c>
+      <c r="B99" t="str">
+        <v>C6</v>
+      </c>
+      <c r="C99" t="str">
+        <v>S62</v>
+      </c>
+      <c r="D99" t="str">
+        <v>집중력 향상 놀이! "안 숨은그림 찾기 1탄"</v>
+      </c>
+      <c r="E99" t="str">
+        <v>nA9I1iv_E8w</v>
+      </c>
+      <c r="F99" t="str">
+        <v>06:46</v>
+      </c>
+      <c r="G99">
+        <v>1278</v>
+      </c>
+      <c r="H99" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I99" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>V0099</v>
+      </c>
+      <c r="B100" t="str">
+        <v>C6</v>
+      </c>
+      <c r="C100" t="str">
+        <v>S62</v>
+      </c>
+      <c r="D100" t="str">
+        <v>[다른그림찾기]💥90초 안에 다른점 3개 찾아주세요! 집중력 향상 두뇌 퀴즈 Find the difference 치매 예방 퀴즈 / 두뇌게임 [틀린그림찾기] 678</v>
+      </c>
+      <c r="E100" t="str">
+        <v>DKA9vzuKFio</v>
+      </c>
+      <c r="F100" t="str">
+        <v>09:26</v>
+      </c>
+      <c r="G100">
+        <v>2249</v>
+      </c>
+      <c r="H100" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I100" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>V0100</v>
+      </c>
+      <c r="B101" t="str">
+        <v>C6</v>
+      </c>
+      <c r="C101" t="str">
+        <v>S62</v>
+      </c>
+      <c r="D101" t="str">
+        <v>【다른그림찾기 | 치매예방】천재도 차이점 3개 중 한 곳은 못 찾습니다! 재밌고 건강한 기억 훈련 퀴즈 문제!【두뇌운동 | Find Difference | 틀린그림찾기】#1602</v>
+      </c>
+      <c r="E101" t="str">
+        <v>0FLsBYtNPkg</v>
+      </c>
+      <c r="F101" t="str">
+        <v>09:26</v>
+      </c>
+      <c r="G101">
+        <v>3220</v>
+      </c>
+      <c r="H101" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I101" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>V0101</v>
+      </c>
+      <c r="B102" t="str">
+        <v>C6</v>
+      </c>
+      <c r="C102" t="str">
+        <v>S63</v>
+      </c>
+      <c r="D102" t="str">
+        <v>넌센스 퀴즈! 최고 재미있는 넌센스모음. 빵빵터지는 웃긴 것만 모은 아재퀴즈! 두뇌 트레이닝! 초성퀴즈ㅣ퍼즐ㅣ그림퀴즈ㅣ넌센스ㅣ초등학생퀴즈ㅣ유머퀴즈</v>
+      </c>
+      <c r="E102" t="str">
+        <v>4FR8-GOwlWs</v>
+      </c>
+      <c r="F102" t="str">
+        <v>04:06</v>
+      </c>
+      <c r="G102">
+        <v>4191</v>
+      </c>
+      <c r="H102" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I102" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>V0102</v>
+      </c>
+      <c r="B103" t="str">
+        <v>C6</v>
+      </c>
+      <c r="C103" t="str">
+        <v>S63</v>
+      </c>
+      <c r="D103" t="str">
+        <v xml:space="preserve">재미있는 넌센스퀴즈 모음 1탄(15문제) #넌센스 #넌센스퀴즈 #아재개그 #유머 #퀴즈 #수수께끼 </v>
+      </c>
+      <c r="E103" t="str">
+        <v>7gjp3gdZE2U</v>
+      </c>
+      <c r="F103" t="str">
+        <v>04:14</v>
+      </c>
+      <c r="G103">
+        <v>5162</v>
+      </c>
+      <c r="H103" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I103" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>V0103</v>
+      </c>
+      <c r="B104" t="str">
+        <v>C6</v>
+      </c>
+      <c r="C104" t="str">
+        <v>S63</v>
+      </c>
+      <c r="D104" t="str">
+        <v>[두뇌퀴즈] "뇌가 똑똑해지는 그림 넌센스 퀴즈 "|수수께끼|아재개그|</v>
+      </c>
+      <c r="E104" t="str">
+        <v>JJRoMT3SiEg</v>
+      </c>
+      <c r="F104" t="str">
+        <v>08:03</v>
+      </c>
+      <c r="G104">
+        <v>6133</v>
+      </c>
+      <c r="H104" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I104" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>V0104</v>
+      </c>
+      <c r="B105" t="str">
+        <v>C6</v>
+      </c>
+      <c r="C105" t="str">
+        <v>S63</v>
+      </c>
+      <c r="D105" t="str">
+        <v>[넌센스] "뇌가 똑똑해지는 그림 넌센스 퀴즈 30"|수수께끼|아재개그|</v>
+      </c>
+      <c r="E105" t="str">
+        <v>zRJj-JwMpcc</v>
+      </c>
+      <c r="F105" t="str">
+        <v>10:54</v>
+      </c>
+      <c r="G105">
+        <v>7104</v>
+      </c>
+      <c r="H105" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="I105" t="str">
+        <v>Y</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I105"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3164,7 +4584,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-22 14:16:53</v>
+        <v>2026-08-22 15:08:39</v>
       </c>
     </row>
     <row r="3">
@@ -3184,7 +4604,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-22 14:16:53</v>
+        <v>2026-08-22 15:08:39</v>
       </c>
     </row>
     <row r="4">
@@ -3204,7 +4624,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-08-22 14:16:53</v>
+        <v>2026-08-22 15:08:39</v>
       </c>
     </row>
   </sheetData>
@@ -3216,7 +4636,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -3249,7 +4669,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="str">
-        <v>V0006,V0010,V0022</v>
+        <v>V0008,V0030,V0062,V0048</v>
       </c>
     </row>
     <row r="3">
@@ -3263,26 +4683,54 @@
         <v>2</v>
       </c>
       <c r="D3" t="str">
-        <v>V0001,V0016,V0026</v>
+        <v>V0009,V0031,V0066,V0049</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>test</v>
+        <v>teacher</v>
       </c>
       <c r="B4" t="str">
-        <v>체력왕 도전</v>
+        <v>리듬 점핑반</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="str">
-        <v>V0017,V0021,V0030</v>
+        <v>V0012,V0078,V0092</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>test</v>
+      </c>
+      <c r="B5" t="str">
+        <v>체력왕 도전</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="str">
+        <v>V0032,V0037,V0042,V0050</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>test</v>
+      </c>
+      <c r="B6" t="str">
+        <v>체력왕 도전</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="str">
+        <v>V0054,V0045,V0098</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/스마트점핑_DB.xlsx
+++ b/스마트점핑_DB.xlsx
@@ -4169,7 +4169,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -4180,6 +4180,7 @@
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4210,6 +4211,9 @@
       <c r="I1" t="str">
         <v>메모</v>
       </c>
+      <c r="J1" t="str">
+        <v>스케줄그룹</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -4239,6 +4243,9 @@
       <c r="I2" t="str">
         <v/>
       </c>
+      <c r="J2" t="str">
+        <v>1학기 기본과정</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -4268,6 +4275,9 @@
       <c r="I3" t="str">
         <v/>
       </c>
+      <c r="J3" t="str">
+        <v>1학기 기본과정</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -4297,6 +4307,9 @@
       <c r="I4" t="str">
         <v/>
       </c>
+      <c r="J4" t="str">
+        <v>리듬 점핑반</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -4326,6 +4339,9 @@
       <c r="I5" t="str">
         <v/>
       </c>
+      <c r="J5" t="str">
+        <v>체력왕 도전</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -4355,6 +4371,9 @@
       <c r="I6" t="str">
         <v/>
       </c>
+      <c r="J6" t="str">
+        <v>체력왕 도전</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -4384,17 +4403,20 @@
       <c r="I7" t="str">
         <v/>
       </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D25"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -4424,7 +4446,7 @@
         <v>김민준</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-15</v>
       </c>
       <c r="D2" t="str">
         <v>출</v>
@@ -4438,7 +4460,7 @@
         <v>이서연</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-15</v>
       </c>
       <c r="D3" t="str">
         <v>출</v>
@@ -4452,7 +4474,7 @@
         <v>박지호</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-15</v>
       </c>
       <c r="D4" t="str">
         <v>출</v>
@@ -4466,7 +4488,7 @@
         <v>최수아</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-15</v>
       </c>
       <c r="D5" t="str">
         <v>결</v>
@@ -4480,7 +4502,7 @@
         <v>정예준</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-15</v>
       </c>
       <c r="D6" t="str">
         <v>출</v>
@@ -4494,7 +4516,7 @@
         <v>강하윤</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-15</v>
       </c>
       <c r="D7" t="str">
         <v>출</v>
@@ -4508,7 +4530,7 @@
         <v>조은우</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-15</v>
       </c>
       <c r="D8" t="str">
         <v>출</v>
@@ -4522,15 +4544,239 @@
         <v>윤채원</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-15</v>
       </c>
       <c r="D9" t="str">
         <v>출</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B10" t="str">
+        <v>김민준</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="D10" t="str">
+        <v>출</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B11" t="str">
+        <v>이서연</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="D11" t="str">
+        <v>출</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B12" t="str">
+        <v>박지호</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="D12" t="str">
+        <v>결</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B13" t="str">
+        <v>최수아</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="D13" t="str">
+        <v>출</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B14" t="str">
+        <v>정예준</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="D14" t="str">
+        <v>지</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B15" t="str">
+        <v>강하윤</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="D15" t="str">
+        <v>출</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B16" t="str">
+        <v>조은우</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="D16" t="str">
+        <v>출</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B17" t="str">
+        <v>윤채원</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="D17" t="str">
+        <v>출</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B18" t="str">
+        <v>김민준</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="D18" t="str">
+        <v>출</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B19" t="str">
+        <v>이서연</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="D19" t="str">
+        <v>결</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B20" t="str">
+        <v>박지호</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="D20" t="str">
+        <v>출</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B21" t="str">
+        <v>최수아</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="D21" t="str">
+        <v>지</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B22" t="str">
+        <v>정예준</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="D22" t="str">
+        <v>출</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B23" t="str">
+        <v>강하윤</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="D23" t="str">
+        <v>출</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B24" t="str">
+        <v>조은우</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="D24" t="str">
+        <v>출</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B25" t="str">
+        <v>윤채원</v>
+      </c>
+      <c r="C25" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="D25" t="str">
+        <v>출</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4584,7 +4830,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-22 15:08:39</v>
+        <v>2026-08-22 15:24:05</v>
       </c>
     </row>
     <row r="3">
@@ -4604,7 +4850,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-22 15:08:39</v>
+        <v>2026-08-22 15:24:05</v>
       </c>
     </row>
     <row r="4">
@@ -4624,7 +4870,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-08-22 15:08:39</v>
+        <v>2026-08-22 15:24:05</v>
       </c>
     </row>
   </sheetData>

--- a/스마트점핑_DB.xlsx
+++ b/스마트점핑_DB.xlsx
@@ -12,6 +12,7 @@
     <sheet name="schedules" sheetId="7" r:id="rId7"/>
     <sheet name="textbooks" sheetId="8" r:id="rId8"/>
     <sheet name="playlists" sheetId="9" r:id="rId9"/>
+    <sheet name="favorites" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -975,6 +976,44 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>소유자</v>
+      </c>
+      <c r="B1" t="str">
+        <v>즐겨찾기영상ID목록</v>
+      </c>
+      <c r="C1" t="str">
+        <v>수정일</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="B2" t="str">
+        <v>V0008,V0016,V0030,V0062,V0085</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-08-22 17:23:49</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I105"/>
@@ -4416,7 +4455,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D28"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -4555,10 +4594,10 @@
         <v>CL001</v>
       </c>
       <c r="B10" t="str">
-        <v>김민준</v>
+        <v>학생</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-08-19</v>
+        <v>2026-08-15</v>
       </c>
       <c r="D10" t="str">
         <v>출</v>
@@ -4569,7 +4608,7 @@
         <v>CL001</v>
       </c>
       <c r="B11" t="str">
-        <v>이서연</v>
+        <v>김민준</v>
       </c>
       <c r="C11" t="str">
         <v>2026-08-19</v>
@@ -4583,13 +4622,13 @@
         <v>CL001</v>
       </c>
       <c r="B12" t="str">
-        <v>박지호</v>
+        <v>이서연</v>
       </c>
       <c r="C12" t="str">
         <v>2026-08-19</v>
       </c>
       <c r="D12" t="str">
-        <v>결</v>
+        <v>출</v>
       </c>
     </row>
     <row r="13">
@@ -4597,13 +4636,13 @@
         <v>CL001</v>
       </c>
       <c r="B13" t="str">
-        <v>최수아</v>
+        <v>박지호</v>
       </c>
       <c r="C13" t="str">
         <v>2026-08-19</v>
       </c>
       <c r="D13" t="str">
-        <v>출</v>
+        <v>결</v>
       </c>
     </row>
     <row r="14">
@@ -4611,13 +4650,13 @@
         <v>CL001</v>
       </c>
       <c r="B14" t="str">
-        <v>정예준</v>
+        <v>최수아</v>
       </c>
       <c r="C14" t="str">
         <v>2026-08-19</v>
       </c>
       <c r="D14" t="str">
-        <v>지</v>
+        <v>출</v>
       </c>
     </row>
     <row r="15">
@@ -4625,13 +4664,13 @@
         <v>CL001</v>
       </c>
       <c r="B15" t="str">
-        <v>강하윤</v>
+        <v>정예준</v>
       </c>
       <c r="C15" t="str">
         <v>2026-08-19</v>
       </c>
       <c r="D15" t="str">
-        <v>출</v>
+        <v>지</v>
       </c>
     </row>
     <row r="16">
@@ -4639,7 +4678,7 @@
         <v>CL001</v>
       </c>
       <c r="B16" t="str">
-        <v>조은우</v>
+        <v>강하윤</v>
       </c>
       <c r="C16" t="str">
         <v>2026-08-19</v>
@@ -4653,7 +4692,7 @@
         <v>CL001</v>
       </c>
       <c r="B17" t="str">
-        <v>윤채원</v>
+        <v>조은우</v>
       </c>
       <c r="C17" t="str">
         <v>2026-08-19</v>
@@ -4667,10 +4706,10 @@
         <v>CL001</v>
       </c>
       <c r="B18" t="str">
-        <v>김민준</v>
+        <v>윤채원</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-19</v>
       </c>
       <c r="D18" t="str">
         <v>출</v>
@@ -4681,13 +4720,13 @@
         <v>CL001</v>
       </c>
       <c r="B19" t="str">
-        <v>이서연</v>
+        <v>학생</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-19</v>
       </c>
       <c r="D19" t="str">
-        <v>결</v>
+        <v>출</v>
       </c>
     </row>
     <row r="20">
@@ -4695,7 +4734,7 @@
         <v>CL001</v>
       </c>
       <c r="B20" t="str">
-        <v>박지호</v>
+        <v>김민준</v>
       </c>
       <c r="C20" t="str">
         <v>2026-08-22</v>
@@ -4709,13 +4748,13 @@
         <v>CL001</v>
       </c>
       <c r="B21" t="str">
-        <v>최수아</v>
+        <v>이서연</v>
       </c>
       <c r="C21" t="str">
         <v>2026-08-22</v>
       </c>
       <c r="D21" t="str">
-        <v>지</v>
+        <v>결</v>
       </c>
     </row>
     <row r="22">
@@ -4723,7 +4762,7 @@
         <v>CL001</v>
       </c>
       <c r="B22" t="str">
-        <v>정예준</v>
+        <v>박지호</v>
       </c>
       <c r="C22" t="str">
         <v>2026-08-22</v>
@@ -4737,13 +4776,13 @@
         <v>CL001</v>
       </c>
       <c r="B23" t="str">
-        <v>강하윤</v>
+        <v>최수아</v>
       </c>
       <c r="C23" t="str">
         <v>2026-08-22</v>
       </c>
       <c r="D23" t="str">
-        <v>출</v>
+        <v>지</v>
       </c>
     </row>
     <row r="24">
@@ -4751,7 +4790,7 @@
         <v>CL001</v>
       </c>
       <c r="B24" t="str">
-        <v>조은우</v>
+        <v>정예준</v>
       </c>
       <c r="C24" t="str">
         <v>2026-08-22</v>
@@ -4765,7 +4804,7 @@
         <v>CL001</v>
       </c>
       <c r="B25" t="str">
-        <v>윤채원</v>
+        <v>강하윤</v>
       </c>
       <c r="C25" t="str">
         <v>2026-08-22</v>
@@ -4774,9 +4813,51 @@
         <v>출</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B26" t="str">
+        <v>조은우</v>
+      </c>
+      <c r="C26" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="D26" t="str">
+        <v>출</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B27" t="str">
+        <v>윤채원</v>
+      </c>
+      <c r="C27" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="D27" t="str">
+        <v>출</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>CL001</v>
+      </c>
+      <c r="B28" t="str">
+        <v>학생</v>
+      </c>
+      <c r="C28" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="D28" t="str">
+        <v>결</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D28"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4830,7 +4911,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-22 15:24:05</v>
+        <v>2026-08-22 17:23:49</v>
       </c>
     </row>
     <row r="3">
@@ -4850,7 +4931,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-22 15:24:05</v>
+        <v>2026-08-22 17:23:49</v>
       </c>
     </row>
     <row r="4">
@@ -4870,7 +4951,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-08-22 15:24:05</v>
+        <v>2026-08-22 17:23:49</v>
       </c>
     </row>
   </sheetData>
